--- a/scripts/ground-truth/_template.xlsx
+++ b/scripts/ground-truth/_template.xlsx
@@ -519,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -527,7 +527,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1215,237 +1217,637 @@
       <c r="A2" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="2:8" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="7"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="7"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="7"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="7"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="7"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="7"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="7"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="7"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="7"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="7"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="7"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="7"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="7"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="7"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="7"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="7"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="7"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="7"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="7"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="7"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="7"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="7"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="7"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="7"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="7"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="7"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="7"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="7"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="7"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="7"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="7"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="7"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="7"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="7"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="7"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="7"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="7"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="7"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="7"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="7"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="7"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="7"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="7"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="7"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="7"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="7"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="7"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="7"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="7"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="7"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="7"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="7"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="7"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="7"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="7"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="7"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="7"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="7"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="7"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="7"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="7"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="7"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="7"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="7"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="7"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="7"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="7"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="7"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="7"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="7"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="7"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="7"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="7"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="7"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="7"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="7"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="7"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="7"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="7"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="7"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="7"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="7"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="7"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="7"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="7"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="7"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="7"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="7"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="7"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="7"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="7"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="7"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="7"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="7"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="7"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="7"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="7"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="7"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="7"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="7"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="7"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="7"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" s="7"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="7"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="7"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="7"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="7"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="7"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" s="7"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="7"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="7"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="7"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="7"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="7"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="7"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="7"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="7"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="7"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="7"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="7"/>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="7"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="7"/>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="7"/>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="7"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="7"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="7"/>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="7"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="7"/>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="7"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="7"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="7"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="7"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="7"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="7"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" s="7"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" s="7"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="7"/>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" s="7"/>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" s="7"/>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="7"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="7"/>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="7"/>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="7"/>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" s="7"/>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" s="7"/>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="7"/>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="7"/>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="7"/>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="7"/>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="7"/>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="7"/>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="7"/>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" s="7"/>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="7"/>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" s="7"/>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" s="7"/>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" s="7"/>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="7"/>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" s="7"/>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" s="7"/>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" s="7"/>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" s="7"/>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" s="7"/>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" s="7"/>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" s="7"/>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="7"/>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" s="7"/>
+    </row>
   </sheetData>
   <dataValidations count="14">
     <dataValidation type="list" allowBlank="1" sqref="B10:B202">
@@ -1565,246 +1967,646 @@
       <c r="A2" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="2:11" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="2:11" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="7"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="7"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="7"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="7"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="7"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="7"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="7"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="7"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="7"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="7"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="7"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="7"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="7"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="7"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="7"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="7"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="7"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="7"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="7"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="7"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="7"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="7"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="7"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="7"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="7"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="7"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="7"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="7"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="7"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="7"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="7"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="7"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="7"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="7"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="7"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="7"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="7"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="7"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="7"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="7"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="7"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="7"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="7"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="7"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="7"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="7"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="7"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="7"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="7"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="7"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="7"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="7"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="7"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="7"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="7"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="7"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="7"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="7"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="7"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="7"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="7"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="7"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="7"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="7"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="7"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="7"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="7"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="7"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="7"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="7"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="7"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" s="7"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="7"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="7"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" s="7"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" s="7"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" s="7"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" s="7"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" s="7"/>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" s="7"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" s="7"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" s="7"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" s="7"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" s="7"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" s="7"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" s="7"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" s="7"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" s="7"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" s="7"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" s="7"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" s="7"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" s="7"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" s="7"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" s="7"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" s="7"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" s="7"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" s="7"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" s="7"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" s="7"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" s="7"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="7"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="7"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" s="7"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="7"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" s="7"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" s="7"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" s="7"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" s="7"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" s="7"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" s="7"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" s="7"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" s="7"/>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144" s="7"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" s="7"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" s="7"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" s="7"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" s="7"/>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" s="7"/>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" s="7"/>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" s="7"/>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" s="7"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" s="7"/>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" s="7"/>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" s="7"/>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" s="7"/>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" s="7"/>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" s="7"/>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" s="7"/>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" s="7"/>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" s="7"/>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" s="7"/>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A163" s="7"/>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A164" s="7"/>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A165" s="7"/>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A166" s="7"/>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A167" s="7"/>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A168" s="7"/>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" s="7"/>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" s="7"/>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" s="7"/>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" s="7"/>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A173" s="7"/>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" s="7"/>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A175" s="7"/>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" s="7"/>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" s="7"/>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A178" s="7"/>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" s="7"/>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" s="7"/>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" s="7"/>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A182" s="7"/>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A183" s="7"/>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A184" s="7"/>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" s="7"/>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" s="7"/>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" s="7"/>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" s="7"/>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A189" s="7"/>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A190" s="7"/>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A191" s="7"/>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A192" s="7"/>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" s="7"/>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" s="7"/>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A195" s="7"/>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A196" s="7"/>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" s="7"/>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A198" s="7"/>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A199" s="7"/>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A200" s="7"/>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A201" s="7"/>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A202" s="7"/>
+    </row>
   </sheetData>
   <dataValidations count="20">
     <dataValidation type="list" allowBlank="1" sqref="B10:B202">
@@ -1895,24 +2697,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -2033,237 +2835,637 @@
       <c r="A17" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K17" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="7"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="7"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="7"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="7"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="7"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="7"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="7"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="7"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="7"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="7"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="7"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="7"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="7"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="7"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="7"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="7"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="7"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="7"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="7"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="7"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="7"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="7"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="7"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="7"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="7"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="7"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="7"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="7"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="7"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="7"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="7"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="7"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="7"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="7"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="7"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="7"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="7"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="7"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="7"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="7"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="7"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="7"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="7"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="7"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="7"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="7"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="7"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="7"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="7"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="7"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="7"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="7"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="7"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="7"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="7"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="7"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="7"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="7"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="7"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="7"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="7"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="7"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="7"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="7"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="7"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="7"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="7"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="7"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="7"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="7"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="7"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="7"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="7"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="7"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="7"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="7"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="7"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="7"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="7"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" s="7"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" s="7"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" s="7"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" s="7"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" s="7"/>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" s="7"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" s="7"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" s="7"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" s="7"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" s="7"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" s="7"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" s="7"/>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" s="7"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="7"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" s="7"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" s="7"/>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" s="7"/>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" s="7"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" s="7"/>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" s="7"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" s="7"/>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" s="7"/>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" s="7"/>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" s="7"/>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" s="7"/>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" s="7"/>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" s="7"/>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" s="7"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" s="7"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" s="7"/>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" s="7"/>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" s="7"/>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A143" s="7"/>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" s="7"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" s="7"/>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" s="7"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" s="7"/>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" s="7"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" s="7"/>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" s="7"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" s="7"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" s="7"/>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" s="7"/>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" s="7"/>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" s="7"/>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" s="7"/>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" s="7"/>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" s="7"/>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" s="7"/>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" s="7"/>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" s="7"/>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" s="7"/>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="7"/>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="7"/>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" s="7"/>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" s="7"/>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" s="7"/>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" s="7"/>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" s="7"/>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" s="7"/>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" s="7"/>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" s="7"/>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" s="7"/>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" s="7"/>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" s="7"/>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" s="7"/>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" s="7"/>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" s="7"/>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" s="7"/>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" s="7"/>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" s="7"/>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" s="7"/>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" s="7"/>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" s="7"/>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" s="7"/>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" s="7"/>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" s="7"/>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" s="7"/>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" s="7"/>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" s="7"/>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" s="7"/>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" s="7"/>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" s="7"/>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" s="7"/>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" s="7"/>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" s="7"/>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" s="7"/>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" s="7"/>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" s="7"/>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" s="7"/>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="7"/>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" s="7"/>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" s="7"/>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" s="7"/>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" s="7"/>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="7"/>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" s="7"/>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" s="7"/>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="7"/>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="7"/>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="7"/>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="7"/>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="7"/>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" s="7"/>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A215" s="7"/>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A216" s="7"/>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A217" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
@@ -2374,231 +3576,631 @@
       <c r="A2" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="2:8" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="2:8" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="7"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="7"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="7"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="7"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="7"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="7"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="7"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="7"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="7"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="7"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="7"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="7"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="7"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="7"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="7"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="7"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="7"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="7"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="7"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="7"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="7"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="7"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="7"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="7"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="7"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="7"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="7"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="7"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="7"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="7"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="7"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="7"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="7"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="7"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="7"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="7"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="7"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="7"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="7"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="7"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="7"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="7"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="7"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="7"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="7"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="7"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="7"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="7"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="7"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="7"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="7"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="7"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="7"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="7"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="7"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="7"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="7"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="7"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="7"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="7"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="7"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="7"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="7"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="7"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="7"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="7"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="7"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="7"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="7"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="7"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="7"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="7"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="7"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="7"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="7"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="7"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="7"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="7"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="7"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="7"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="7"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="7"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="7"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="7"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="7"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="7"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="7"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="7"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="7"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="7"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="7"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="7"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="7"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="7"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="7"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="7"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="7"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="7"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="7"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="7"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="7"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="7"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" s="7"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="7"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="7"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="7"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="7"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="7"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" s="7"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="7"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="7"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="7"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="7"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="7"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="7"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="7"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="7"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="7"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="7"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="7"/>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="7"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="7"/>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="7"/>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="7"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="7"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="7"/>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="7"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="7"/>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="7"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="7"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="7"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="7"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="7"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="7"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" s="7"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" s="7"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="7"/>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" s="7"/>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" s="7"/>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="7"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="7"/>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="7"/>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="7"/>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" s="7"/>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" s="7"/>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="7"/>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="7"/>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="7"/>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="7"/>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="7"/>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="7"/>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="7"/>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" s="7"/>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="7"/>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" s="7"/>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" s="7"/>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" s="7"/>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="7"/>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" s="7"/>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" s="7"/>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" s="7"/>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" s="7"/>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" s="7"/>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" s="7"/>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" s="7"/>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="7"/>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" s="7"/>
+    </row>
   </sheetData>
   <dataValidations count="14">
     <dataValidation type="list" allowBlank="1" sqref="B10:B202">
@@ -2697,228 +4299,628 @@
       <c r="A2" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="2:7" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="7"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="7"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="7"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="7"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="7"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="7"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="7"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="7"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="7"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="7"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="7"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="7"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="7"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="7"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="7"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="7"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="7"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="7"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="7"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="7"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="7"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="7"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="7"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="7"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="7"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="7"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="7"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="7"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="7"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="7"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="7"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="7"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="7"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="7"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="7"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="7"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="7"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="7"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="7"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="7"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="7"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="7"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="7"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="7"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="7"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="7"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="7"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="7"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="7"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="7"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="7"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="7"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="7"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="7"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="7"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="7"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="7"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="7"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="7"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="7"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="7"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="7"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="7"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="7"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="7"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="7"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="7"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="7"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="7"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="7"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="7"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="7"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="7"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="7"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="7"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="7"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="7"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="7"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="7"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="7"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="7"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="7"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="7"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="7"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="7"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="7"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="7"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="7"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="7"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="7"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="7"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="7"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="7"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="7"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="7"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="7"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="7"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="7"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="7"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="7"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="7"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="7"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="7"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="7"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="7"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="7"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="7"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="7"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="7"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="7"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="7"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="7"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="7"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="7"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="7"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="7"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="7"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="7"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="7"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="7"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="7"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="7"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="7"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="7"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="7"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="7"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="7"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="7"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="7"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="7"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="7"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="7"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="7"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="7"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="7"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="7"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="7"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="7"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="7"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="7"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="7"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="7"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" s="7"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="7"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="7"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="7"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="7"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="7"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="7"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="7"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="7"/>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="7"/>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" s="7"/>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="7"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="7"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" s="7"/>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="7"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="7"/>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="7"/>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" s="7"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" s="7"/>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" s="7"/>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" s="7"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" s="7"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="7"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201" s="7"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" s="7"/>
+    </row>
   </sheetData>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" sqref="B10:B202">
@@ -2999,219 +5001,619 @@
       <c r="A2" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="7"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="7"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="7"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="7"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="7"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="7"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="7"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="7"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="7"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="7"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="7"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="7"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="7"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="7"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="7"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="7"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="7"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="7"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="7"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="7"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="7"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="7"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="7"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="7"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="7"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="7"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="7"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="7"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="7"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="7"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="7"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="7"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="7"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="7"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="7"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="7"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="7"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="7"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="7"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="7"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="7"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="7"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="7"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="7"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="7"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="7"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="7"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="7"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="7"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="7"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="7"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="7"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="7"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="7"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="7"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="7"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="7"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="7"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="7"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="7"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="7"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="7"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="7"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="7"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="7"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="7"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="7"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="7"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="7"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="7"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="7"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="7"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="7"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="7"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="7"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="7"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="7"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="7"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="7"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="7"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="7"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="7"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="7"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="7"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="7"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="7"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="7"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="7"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="7"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="7"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="7"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="7"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="7"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="7"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="7"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="7"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="7"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="7"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="7"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="7"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="7"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="7"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="7"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="7"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="7"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="7"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="7"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="7"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="7"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="7"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="7"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="7"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="7"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="7"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" s="7"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="7"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" s="7"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" s="7"/>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" s="7"/>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" s="7"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="7"/>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="7"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" s="7"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" s="7"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="7"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" s="7"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" s="7"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" s="7"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" s="7"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" s="7"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" s="7"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" s="7"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" s="7"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" s="7"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" s="7"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" s="7"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" s="7"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" s="7"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" s="7"/>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" s="7"/>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" s="7"/>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" s="7"/>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" s="7"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" s="7"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" s="7"/>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" s="7"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" s="7"/>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" s="7"/>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="7"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" s="7"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="7"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="7"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="7"/>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="7"/>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="7"/>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="7"/>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="7"/>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" s="7"/>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="7"/>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="7"/>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="7"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="7"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="7"/>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="7"/>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="7"/>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="7"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="7"/>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" sqref="B10:B202">

--- a/scripts/ground-truth/_template.xlsx
+++ b/scripts/ground-truth/_template.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="103">
   <si>
     <t>STIX Match Ground-Truth Tagger</t>
   </si>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">     • 1v1s — high-value moments worth a dedicated row</t>
   </si>
   <si>
-    <t>4. The first row beneath the header on each sheet is a SAMPLE — overwrite or delete it.</t>
+    <t>4. The data sheets are EMPTY — start typing on row 2 (the row directly below the headers). Format examples are below if you need them.</t>
   </si>
   <si>
     <t>5. Save the file. Run:  node scripts/excel-to-ground-truth.js scripts/ground-truth/&lt;match-name&gt;.xlsx</t>
@@ -83,6 +83,27 @@
     <t>Tab colours: red=Goals, green=Saves, blue=Distribution, orange=Crosses, purple=Sweeper, gold=1v1s, grey=metadata/this README.</t>
   </si>
   <si>
+    <t>FORMAT EXAMPLES (copy the IDEA, not the literal row, into the relevant sheet):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Goals: 4:05 | 1 | Us | Open play | Rebound | 6-Yard Box | Low | Centre | Right-side initial shot saved, follow-up tap-in central. | Opp GK was on ground from initial save. | (notes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Saves: 24:47 | 1 | Central Distance | Foot | Yes | Parry | Yes | Corner | C | Low | GK Right | Driven shot from outside the box, central. | Strong parry — full extension dive to the right. | (notes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Distribution: 14:32 | 1 | Backpass | Pass | Yes | Yes | Switch wide | Left | Defender | Clean | Recycled possession to LCB under high press.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Crosses: 36:18 | 2 | Corner Right | Whipped | Near post | Punch | Edge of 6yd | Punched away | Two-fisted punch under pressure from two attackers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Sweeper: 28:15 | 1 | Clearance | 5–15 yards out | Yes | 1 attacker | Cleared safely | Read the through ball early.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1v1s: 52:17 | 2 | 1v1 faced | Conceded | Through ball over the top, GK rushed off line, attacker rounded him.</t>
+  </si>
+  <si>
     <t>Field</t>
   </si>
   <si>
@@ -206,36 +227,6 @@
     <t>GK observations</t>
   </si>
   <si>
-    <t>4:05</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Us</t>
-  </si>
-  <si>
-    <t>Open play</t>
-  </si>
-  <si>
-    <t>Rebound</t>
-  </si>
-  <si>
-    <t>6-Yard Box</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Centre</t>
-  </si>
-  <si>
-    <t>Right-side initial shot saved by opp GK, follow-up tap-in central.</t>
-  </si>
-  <si>
-    <t>Opp GK was on ground from initial save, could not recover for the rebound.</t>
-  </si>
-  <si>
     <t>Shot origin</t>
   </si>
   <si>
@@ -254,36 +245,6 @@
     <t>Body zone (A/B/C)</t>
   </si>
   <si>
-    <t>24:47</t>
-  </si>
-  <si>
-    <t>Central Distance</t>
-  </si>
-  <si>
-    <t>Foot</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Parry</t>
-  </si>
-  <si>
-    <t>Corner</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>GK Right</t>
-  </si>
-  <si>
-    <t>Driven shot from outside the box, central, aimed at the bottom-right corner.</t>
-  </si>
-  <si>
-    <t>Strong parry — full extension dive to the right, palm strike, ball deflected wide for a corner.</t>
-  </si>
-  <si>
     <t>QUICK TOTALS — fill these IN PLACE OF logging every event if you do not want to tag row-by-row.</t>
   </si>
   <si>
@@ -344,30 +305,6 @@
     <t>First touch</t>
   </si>
   <si>
-    <t>14:32</t>
-  </si>
-  <si>
-    <t>Backpass</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>Switch wide</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>Defender</t>
-  </si>
-  <si>
-    <t>Clean</t>
-  </si>
-  <si>
-    <t>Recycled possession to LCB under high press; built out from the back successfully.</t>
-  </si>
-  <si>
     <t>Side</t>
   </si>
   <si>
@@ -380,33 +317,6 @@
     <t>GK starting pos</t>
   </si>
   <si>
-    <t>36:18</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Corner Right</t>
-  </si>
-  <si>
-    <t>Whipped</t>
-  </si>
-  <si>
-    <t>Near post</t>
-  </si>
-  <si>
-    <t>Punch</t>
-  </si>
-  <si>
-    <t>Edge of 6yd</t>
-  </si>
-  <si>
-    <t>Punched away</t>
-  </si>
-  <si>
-    <t>Two-fisted punch under pressure from two attackers; cleared 25 yards.</t>
-  </si>
-  <si>
     <t>Action</t>
   </si>
   <si>
@@ -416,37 +326,7 @@
     <t>Pressure</t>
   </si>
   <si>
-    <t>28:15</t>
-  </si>
-  <si>
-    <t>Clearance</t>
-  </si>
-  <si>
-    <t>5–15 yards out</t>
-  </si>
-  <si>
-    <t>1 attacker</t>
-  </si>
-  <si>
-    <t>Cleared safely</t>
-  </si>
-  <si>
-    <t>Read the through ball early; one-touch clearance to the right wing.</t>
-  </si>
-  <si>
     <t>Event type</t>
-  </si>
-  <si>
-    <t>52:17</t>
-  </si>
-  <si>
-    <t>1v1 faced</t>
-  </si>
-  <si>
-    <t>Conceded</t>
-  </si>
-  <si>
-    <t>Through ball over the top, GK rushed off line, attacker rounded him to score into empty net. Sweeper-keeper action with poor angle.</t>
   </si>
 </sst>
 </file>
@@ -480,7 +360,7 @@
       <color rgb="FF666666"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -490,11 +370,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E2A32"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -519,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -527,8 +402,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -873,7 +746,7 @@
   <sheetPr>
     <tabColor rgb="FF888888"/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -992,6 +865,51 @@
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1015,110 +933,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
+        <v>53</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B12">
         <v>4</v>
@@ -1126,7 +1044,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1134,13 +1052,13 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1180,673 +1098,641 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>1</v>
-      </c>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
+      <c r="A3" s="5"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
+      <c r="A5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
+      <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
+      <c r="A7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
+      <c r="A8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
+      <c r="A9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
+      <c r="A10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
+      <c r="A11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
+      <c r="A13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
+      <c r="A14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
+      <c r="A15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
+      <c r="A17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
+      <c r="A18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
+      <c r="A19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
+      <c r="A20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
+      <c r="A21" s="5"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
+      <c r="A22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
+      <c r="A23" s="5"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
+      <c r="A24" s="5"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
+      <c r="A25" s="5"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
+      <c r="A26" s="5"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
+      <c r="A27" s="5"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
+      <c r="A28" s="5"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
+      <c r="A29" s="5"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
+      <c r="A30" s="5"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
+      <c r="A31" s="5"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
+      <c r="A33" s="5"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
+      <c r="A34" s="5"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
+      <c r="A35" s="5"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
+      <c r="A40" s="5"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
+      <c r="A41" s="5"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
+      <c r="A42" s="5"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
+      <c r="A43" s="5"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
+      <c r="A44" s="5"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
+      <c r="A45" s="5"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
+      <c r="A46" s="5"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
+      <c r="A47" s="5"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
+      <c r="A48" s="5"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
+      <c r="A49" s="5"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
+      <c r="A50" s="5"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
+      <c r="A51" s="5"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
+      <c r="A52" s="5"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="7"/>
+      <c r="A53" s="5"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="7"/>
+      <c r="A54" s="5"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="7"/>
+      <c r="A55" s="5"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="7"/>
+      <c r="A56" s="5"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="7"/>
+      <c r="A57" s="5"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
+      <c r="A58" s="5"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="7"/>
+      <c r="A59" s="5"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
+      <c r="A60" s="5"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
+      <c r="A61" s="5"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="7"/>
+      <c r="A62" s="5"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="7"/>
+      <c r="A63" s="5"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="7"/>
+      <c r="A64" s="5"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="7"/>
+      <c r="A65" s="5"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="7"/>
+      <c r="A66" s="5"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="7"/>
+      <c r="A67" s="5"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="7"/>
+      <c r="A68" s="5"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="7"/>
+      <c r="A69" s="5"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="7"/>
+      <c r="A70" s="5"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="7"/>
+      <c r="A71" s="5"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
+      <c r="A72" s="5"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="7"/>
+      <c r="A73" s="5"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
+      <c r="A74" s="5"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="7"/>
+      <c r="A75" s="5"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="7"/>
+      <c r="A76" s="5"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
+      <c r="A77" s="5"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="7"/>
+      <c r="A78" s="5"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="7"/>
+      <c r="A79" s="5"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="7"/>
+      <c r="A80" s="5"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="7"/>
+      <c r="A81" s="5"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="7"/>
+      <c r="A82" s="5"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="7"/>
+      <c r="A83" s="5"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="7"/>
+      <c r="A84" s="5"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="7"/>
+      <c r="A85" s="5"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="7"/>
+      <c r="A86" s="5"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="7"/>
+      <c r="A87" s="5"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="7"/>
+      <c r="A88" s="5"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="7"/>
+      <c r="A89" s="5"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="7"/>
+      <c r="A90" s="5"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="7"/>
+      <c r="A91" s="5"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="7"/>
+      <c r="A92" s="5"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="7"/>
+      <c r="A93" s="5"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="7"/>
+      <c r="A94" s="5"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="7"/>
+      <c r="A95" s="5"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="7"/>
+      <c r="A96" s="5"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="7"/>
+      <c r="A97" s="5"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="7"/>
+      <c r="A98" s="5"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="7"/>
+      <c r="A99" s="5"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="7"/>
+      <c r="A100" s="5"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="7"/>
+      <c r="A101" s="5"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="7"/>
+      <c r="A102" s="5"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="7"/>
+      <c r="A103" s="5"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="7"/>
+      <c r="A104" s="5"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="7"/>
+      <c r="A105" s="5"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="7"/>
+      <c r="A106" s="5"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="7"/>
+      <c r="A107" s="5"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="7"/>
+      <c r="A108" s="5"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="7"/>
+      <c r="A109" s="5"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="7"/>
+      <c r="A110" s="5"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="7"/>
+      <c r="A111" s="5"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="7"/>
+      <c r="A112" s="5"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="7"/>
+      <c r="A113" s="5"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="7"/>
+      <c r="A114" s="5"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="7"/>
+      <c r="A115" s="5"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="7"/>
+      <c r="A116" s="5"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="7"/>
+      <c r="A117" s="5"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="7"/>
+      <c r="A118" s="5"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="7"/>
+      <c r="A119" s="5"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="7"/>
+      <c r="A120" s="5"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="7"/>
+      <c r="A121" s="5"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="7"/>
+      <c r="A122" s="5"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="7"/>
+      <c r="A123" s="5"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="7"/>
+      <c r="A124" s="5"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="7"/>
+      <c r="A125" s="5"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="7"/>
+      <c r="A126" s="5"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="7"/>
+      <c r="A127" s="5"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="7"/>
+      <c r="A128" s="5"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="7"/>
+      <c r="A129" s="5"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="7"/>
+      <c r="A130" s="5"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="7"/>
+      <c r="A131" s="5"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="7"/>
+      <c r="A132" s="5"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="7"/>
+      <c r="A133" s="5"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="7"/>
+      <c r="A134" s="5"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="7"/>
+      <c r="A135" s="5"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="7"/>
+      <c r="A136" s="5"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="7"/>
+      <c r="A137" s="5"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="7"/>
+      <c r="A138" s="5"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="7"/>
+      <c r="A139" s="5"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="7"/>
+      <c r="A140" s="5"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="7"/>
+      <c r="A141" s="5"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="7"/>
+      <c r="A142" s="5"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="7"/>
+      <c r="A143" s="5"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="7"/>
+      <c r="A144" s="5"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="7"/>
+      <c r="A145" s="5"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="7"/>
+      <c r="A146" s="5"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="7"/>
+      <c r="A147" s="5"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="7"/>
+      <c r="A148" s="5"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="7"/>
+      <c r="A149" s="5"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="7"/>
+      <c r="A150" s="5"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="7"/>
+      <c r="A151" s="5"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="7"/>
+      <c r="A152" s="5"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="7"/>
+      <c r="A153" s="5"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="7"/>
+      <c r="A154" s="5"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="7"/>
+      <c r="A155" s="5"/>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="7"/>
+      <c r="A156" s="5"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="7"/>
+      <c r="A157" s="5"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="7"/>
+      <c r="A158" s="5"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="7"/>
+      <c r="A159" s="5"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="7"/>
+      <c r="A160" s="5"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="7"/>
+      <c r="A161" s="5"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="7"/>
+      <c r="A162" s="5"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="7"/>
+      <c r="A163" s="5"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" s="7"/>
+      <c r="A164" s="5"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="7"/>
+      <c r="A165" s="5"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="7"/>
+      <c r="A166" s="5"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="7"/>
+      <c r="A167" s="5"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="7"/>
+      <c r="A168" s="5"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" s="7"/>
+      <c r="A169" s="5"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="7"/>
+      <c r="A170" s="5"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="7"/>
+      <c r="A171" s="5"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="7"/>
+      <c r="A172" s="5"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" s="7"/>
+      <c r="A173" s="5"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="7"/>
+      <c r="A174" s="5"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="7"/>
+      <c r="A175" s="5"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="7"/>
+      <c r="A176" s="5"/>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="7"/>
+      <c r="A177" s="5"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" s="7"/>
+      <c r="A178" s="5"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" s="7"/>
+      <c r="A179" s="5"/>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="7"/>
+      <c r="A180" s="5"/>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A181" s="7"/>
+      <c r="A181" s="5"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A182" s="7"/>
+      <c r="A182" s="5"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="7"/>
+      <c r="A183" s="5"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="7"/>
+      <c r="A184" s="5"/>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="7"/>
+      <c r="A185" s="5"/>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="7"/>
+      <c r="A186" s="5"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="7"/>
+      <c r="A187" s="5"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="7"/>
+      <c r="A188" s="5"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="7"/>
+      <c r="A189" s="5"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="7"/>
+      <c r="A190" s="5"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="7"/>
+      <c r="A191" s="5"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="7"/>
+      <c r="A192" s="5"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="7"/>
+      <c r="A193" s="5"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="7"/>
+      <c r="A194" s="5"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="7"/>
+      <c r="A195" s="5"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="7"/>
+      <c r="A196" s="5"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="7"/>
+      <c r="A197" s="5"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A198" s="7"/>
+      <c r="A198" s="5"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="7"/>
+      <c r="A199" s="5"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A200" s="7"/>
+      <c r="A200" s="5"/>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A201" s="7"/>
+      <c r="A201" s="5"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="7"/>
+      <c r="A202" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="14">
@@ -1921,691 +1807,650 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="J1" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>1</v>
-      </c>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
+      <c r="A3" s="5"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
+      <c r="A5" s="5"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
+      <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
+      <c r="A7" s="5"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
+      <c r="A8" s="5"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
+      <c r="A9" s="5"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
+      <c r="A10" s="5"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
+      <c r="A11" s="5"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
+      <c r="A13" s="5"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
+      <c r="A14" s="5"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
+      <c r="A15" s="5"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
+      <c r="A17" s="5"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
+      <c r="A18" s="5"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
+      <c r="A19" s="5"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
+      <c r="A20" s="5"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
+      <c r="A21" s="5"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
+      <c r="A22" s="5"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
+      <c r="A23" s="5"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
+      <c r="A24" s="5"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
+      <c r="A25" s="5"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
+      <c r="A26" s="5"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
+      <c r="A27" s="5"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
+      <c r="A28" s="5"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
+      <c r="A29" s="5"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
+      <c r="A30" s="5"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
+      <c r="A31" s="5"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
+      <c r="A33" s="5"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
+      <c r="A34" s="5"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
+      <c r="A35" s="5"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
+      <c r="A40" s="5"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
+      <c r="A41" s="5"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
+      <c r="A42" s="5"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
+      <c r="A43" s="5"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
+      <c r="A44" s="5"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
+      <c r="A45" s="5"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
+      <c r="A46" s="5"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
+      <c r="A47" s="5"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
+      <c r="A48" s="5"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
+      <c r="A49" s="5"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
+      <c r="A50" s="5"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
+      <c r="A51" s="5"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
+      <c r="A52" s="5"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="7"/>
+      <c r="A53" s="5"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="7"/>
+      <c r="A54" s="5"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="7"/>
+      <c r="A55" s="5"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="7"/>
+      <c r="A56" s="5"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="7"/>
+      <c r="A57" s="5"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
+      <c r="A58" s="5"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="7"/>
+      <c r="A59" s="5"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
+      <c r="A60" s="5"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
+      <c r="A61" s="5"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="7"/>
+      <c r="A62" s="5"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="7"/>
+      <c r="A63" s="5"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="7"/>
+      <c r="A64" s="5"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="7"/>
+      <c r="A65" s="5"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="7"/>
+      <c r="A66" s="5"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="7"/>
+      <c r="A67" s="5"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="7"/>
+      <c r="A68" s="5"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="7"/>
+      <c r="A69" s="5"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="7"/>
+      <c r="A70" s="5"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="7"/>
+      <c r="A71" s="5"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
+      <c r="A72" s="5"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="7"/>
+      <c r="A73" s="5"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
+      <c r="A74" s="5"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="7"/>
+      <c r="A75" s="5"/>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="7"/>
+      <c r="A76" s="5"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
+      <c r="A77" s="5"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="7"/>
+      <c r="A78" s="5"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="7"/>
+      <c r="A79" s="5"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="7"/>
+      <c r="A80" s="5"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="7"/>
+      <c r="A81" s="5"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="7"/>
+      <c r="A82" s="5"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="7"/>
+      <c r="A83" s="5"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="7"/>
+      <c r="A84" s="5"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="7"/>
+      <c r="A85" s="5"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="7"/>
+      <c r="A86" s="5"/>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="7"/>
+      <c r="A87" s="5"/>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" s="7"/>
+      <c r="A88" s="5"/>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="7"/>
+      <c r="A89" s="5"/>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" s="7"/>
+      <c r="A90" s="5"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="7"/>
+      <c r="A91" s="5"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="7"/>
+      <c r="A92" s="5"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" s="7"/>
+      <c r="A93" s="5"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" s="7"/>
+      <c r="A94" s="5"/>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="7"/>
+      <c r="A95" s="5"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="7"/>
+      <c r="A96" s="5"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="7"/>
+      <c r="A97" s="5"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="7"/>
+      <c r="A98" s="5"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="7"/>
+      <c r="A99" s="5"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="7"/>
+      <c r="A100" s="5"/>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="7"/>
+      <c r="A101" s="5"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="7"/>
+      <c r="A102" s="5"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="7"/>
+      <c r="A103" s="5"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="7"/>
+      <c r="A104" s="5"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="7"/>
+      <c r="A105" s="5"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="7"/>
+      <c r="A106" s="5"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="7"/>
+      <c r="A107" s="5"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="7"/>
+      <c r="A108" s="5"/>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="7"/>
+      <c r="A109" s="5"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="7"/>
+      <c r="A110" s="5"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="7"/>
+      <c r="A111" s="5"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="7"/>
+      <c r="A112" s="5"/>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="7"/>
+      <c r="A113" s="5"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="7"/>
+      <c r="A114" s="5"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="7"/>
+      <c r="A115" s="5"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" s="7"/>
+      <c r="A116" s="5"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" s="7"/>
+      <c r="A117" s="5"/>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="7"/>
+      <c r="A118" s="5"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" s="7"/>
+      <c r="A119" s="5"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="7"/>
+      <c r="A120" s="5"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="7"/>
+      <c r="A121" s="5"/>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" s="7"/>
+      <c r="A122" s="5"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="7"/>
+      <c r="A123" s="5"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" s="7"/>
+      <c r="A124" s="5"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" s="7"/>
+      <c r="A125" s="5"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A126" s="7"/>
+      <c r="A126" s="5"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A127" s="7"/>
+      <c r="A127" s="5"/>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128" s="7"/>
+      <c r="A128" s="5"/>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A129" s="7"/>
+      <c r="A129" s="5"/>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A130" s="7"/>
+      <c r="A130" s="5"/>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A131" s="7"/>
+      <c r="A131" s="5"/>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A132" s="7"/>
+      <c r="A132" s="5"/>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A133" s="7"/>
+      <c r="A133" s="5"/>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A134" s="7"/>
+      <c r="A134" s="5"/>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A135" s="7"/>
+      <c r="A135" s="5"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A136" s="7"/>
+      <c r="A136" s="5"/>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A137" s="7"/>
+      <c r="A137" s="5"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A138" s="7"/>
+      <c r="A138" s="5"/>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A139" s="7"/>
+      <c r="A139" s="5"/>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A140" s="7"/>
+      <c r="A140" s="5"/>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A141" s="7"/>
+      <c r="A141" s="5"/>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A142" s="7"/>
+      <c r="A142" s="5"/>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A143" s="7"/>
+      <c r="A143" s="5"/>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A144" s="7"/>
+      <c r="A144" s="5"/>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A145" s="7"/>
+      <c r="A145" s="5"/>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A146" s="7"/>
+      <c r="A146" s="5"/>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147" s="7"/>
+      <c r="A147" s="5"/>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A148" s="7"/>
+      <c r="A148" s="5"/>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A149" s="7"/>
+      <c r="A149" s="5"/>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A150" s="7"/>
+      <c r="A150" s="5"/>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A151" s="7"/>
+      <c r="A151" s="5"/>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A152" s="7"/>
+      <c r="A152" s="5"/>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A153" s="7"/>
+      <c r="A153" s="5"/>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A154" s="7"/>
+      <c r="A154" s="5"/>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A155" s="7"/>
+      <c r="A155" s="5"/>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A156" s="7"/>
+      <c r="A156" s="5"/>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A157" s="7"/>
+      <c r="A157" s="5"/>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A158" s="7"/>
+      <c r="A158" s="5"/>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A159" s="7"/>
+      <c r="A159" s="5"/>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A160" s="7"/>
+      <c r="A160" s="5"/>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A161" s="7"/>
+      <c r="A161" s="5"/>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A162" s="7"/>
+      <c r="A162" s="5"/>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A163" s="7"/>
+      <c r="A163" s="5"/>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A164" s="7"/>
+      <c r="A164" s="5"/>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A165" s="7"/>
+      <c r="A165" s="5"/>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A166" s="7"/>
+      <c r="A166" s="5"/>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A167" s="7"/>
+      <c r="A167" s="5"/>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A168" s="7"/>
+      <c r="A168" s="5"/>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A169" s="7"/>
+      <c r="A169" s="5"/>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A170" s="7"/>
+      <c r="A170" s="5"/>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A171" s="7"/>
+      <c r="A171" s="5"/>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A172" s="7"/>
+      <c r="A172" s="5"/>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A173" s="7"/>
+      <c r="A173" s="5"/>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A174" s="7"/>
+      <c r="A174" s="5"/>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A175" s="7"/>
+      <c r="A175" s="5"/>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A176" s="7"/>
+      <c r="A176" s="5"/>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A177" s="7"/>
+      <c r="A177" s="5"/>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A178" s="7"/>
+      <c r="A178" s="5"/>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A179" s="7"/>
+      <c r="A179" s="5"/>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A180" s="7"/>
+      <c r="A180" s="5"/>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A181" s="7"/>
+      <c r="A181" s="5"/>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A182" s="7"/>
+      <c r="A182" s="5"/>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A183" s="7"/>
+      <c r="A183" s="5"/>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A184" s="7"/>
+      <c r="A184" s="5"/>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A185" s="7"/>
+      <c r="A185" s="5"/>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A186" s="7"/>
+      <c r="A186" s="5"/>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A187" s="7"/>
+      <c r="A187" s="5"/>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A188" s="7"/>
+      <c r="A188" s="5"/>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A189" s="7"/>
+      <c r="A189" s="5"/>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A190" s="7"/>
+      <c r="A190" s="5"/>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A191" s="7"/>
+      <c r="A191" s="5"/>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A192" s="7"/>
+      <c r="A192" s="5"/>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A193" s="7"/>
+      <c r="A193" s="5"/>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A194" s="7"/>
+      <c r="A194" s="5"/>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A195" s="7"/>
+      <c r="A195" s="5"/>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A196" s="7"/>
+      <c r="A196" s="5"/>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A197" s="7"/>
+      <c r="A197" s="5"/>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A198" s="7"/>
+      <c r="A198" s="5"/>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A199" s="7"/>
+      <c r="A199" s="5"/>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A200" s="7"/>
+      <c r="A200" s="5"/>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A201" s="7"/>
+      <c r="A201" s="5"/>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A202" s="7"/>
+      <c r="A202" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="20">
@@ -2697,28 +2542,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="A1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
+      <c r="A2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -2726,7 +2571,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -2734,7 +2579,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -2742,7 +2587,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -2750,7 +2595,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
@@ -2758,7 +2603,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -2766,7 +2611,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
@@ -2774,7 +2619,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
@@ -2782,7 +2627,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2790,7 +2635,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
@@ -2798,673 +2643,641 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>115</v>
-      </c>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
+      <c r="A18" s="5"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
+      <c r="A19" s="5"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
+      <c r="A20" s="5"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
+      <c r="A21" s="5"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
+      <c r="A22" s="5"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
+      <c r="A23" s="5"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
+      <c r="A24" s="5"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
+      <c r="A25" s="5"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
+      <c r="A26" s="5"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
+      <c r="A27" s="5"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
+      <c r="A28" s="5"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
+      <c r="A29" s="5"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
+      <c r="A30" s="5"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
+      <c r="A31" s="5"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
+      <c r="A33" s="5"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
+      <c r="A34" s="5"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
+      <c r="A35" s="5"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
+      <c r="A40" s="5"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
+      <c r="A41" s="5"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
+      <c r="A42" s="5"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
+      <c r="A43" s="5"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
+      <c r="A44" s="5"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
+      <c r="A45" s="5"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
+      <c r="A46" s="5"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
+      <c r="A47" s="5"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
+      <c r="A48" s="5"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
+      <c r="A49" s="5"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
+      <c r="A50" s="5"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
+      <c r="A51" s="5"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
+      <c r="A52" s="5"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="7"/>
+      <c r="A53" s="5"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="7"/>
+      <c r="A54" s="5"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="7"/>
+      <c r="A55" s="5"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="7"/>
+      <c r="A56" s="5"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="7"/>
+      <c r="A57" s="5"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
+      <c r="A58" s="5"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="7"/>
+      <c r="A59" s="5"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
+      <c r="A60" s="5"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
+      <c r="A61" s="5"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="7"/>
+      <c r="A62" s="5"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="7"/>
+      <c r="A63" s="5"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="7"/>
+      <c r="A64" s="5"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="7"/>
+      <c r="A65" s="5"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="7"/>
+      <c r="A66" s="5"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="7"/>
+      <c r="A67" s="5"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="7"/>
+      <c r="A68" s="5"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="7"/>
+      <c r="A69" s="5"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="7"/>
+      <c r="A70" s="5"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="7"/>
+      <c r="A71" s="5"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
+      <c r="A72" s="5"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="7"/>
+      <c r="A73" s="5"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
+      <c r="A74" s="5"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="7"/>
+      <c r="A75" s="5"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="7"/>
+      <c r="A76" s="5"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
+      <c r="A77" s="5"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="7"/>
+      <c r="A78" s="5"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="7"/>
+      <c r="A79" s="5"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="7"/>
+      <c r="A80" s="5"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="7"/>
+      <c r="A81" s="5"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="7"/>
+      <c r="A82" s="5"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="7"/>
+      <c r="A83" s="5"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="7"/>
+      <c r="A84" s="5"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="7"/>
+      <c r="A85" s="5"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="7"/>
+      <c r="A86" s="5"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="7"/>
+      <c r="A87" s="5"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="7"/>
+      <c r="A88" s="5"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="7"/>
+      <c r="A89" s="5"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="7"/>
+      <c r="A90" s="5"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="7"/>
+      <c r="A91" s="5"/>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="7"/>
+      <c r="A92" s="5"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="7"/>
+      <c r="A93" s="5"/>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="7"/>
+      <c r="A94" s="5"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="7"/>
+      <c r="A95" s="5"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="7"/>
+      <c r="A96" s="5"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" s="7"/>
+      <c r="A97" s="5"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" s="7"/>
+      <c r="A98" s="5"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" s="7"/>
+      <c r="A99" s="5"/>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="7"/>
+      <c r="A100" s="5"/>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A101" s="7"/>
+      <c r="A101" s="5"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" s="7"/>
+      <c r="A102" s="5"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" s="7"/>
+      <c r="A103" s="5"/>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" s="7"/>
+      <c r="A104" s="5"/>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" s="7"/>
+      <c r="A105" s="5"/>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="7"/>
+      <c r="A106" s="5"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" s="7"/>
+      <c r="A107" s="5"/>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" s="7"/>
+      <c r="A108" s="5"/>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A109" s="7"/>
+      <c r="A109" s="5"/>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A110" s="7"/>
+      <c r="A110" s="5"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" s="7"/>
+      <c r="A111" s="5"/>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="7"/>
+      <c r="A112" s="5"/>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" s="7"/>
+      <c r="A113" s="5"/>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" s="7"/>
+      <c r="A114" s="5"/>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A115" s="7"/>
+      <c r="A115" s="5"/>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" s="7"/>
+      <c r="A116" s="5"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" s="7"/>
+      <c r="A117" s="5"/>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A118" s="7"/>
+      <c r="A118" s="5"/>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A119" s="7"/>
+      <c r="A119" s="5"/>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" s="7"/>
+      <c r="A120" s="5"/>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A121" s="7"/>
+      <c r="A121" s="5"/>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A122" s="7"/>
+      <c r="A122" s="5"/>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A123" s="7"/>
+      <c r="A123" s="5"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A124" s="7"/>
+      <c r="A124" s="5"/>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A125" s="7"/>
+      <c r="A125" s="5"/>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A126" s="7"/>
+      <c r="A126" s="5"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" s="7"/>
+      <c r="A127" s="5"/>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" s="7"/>
+      <c r="A128" s="5"/>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="7"/>
+      <c r="A129" s="5"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A130" s="7"/>
+      <c r="A130" s="5"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A131" s="7"/>
+      <c r="A131" s="5"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A132" s="7"/>
+      <c r="A132" s="5"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A133" s="7"/>
+      <c r="A133" s="5"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" s="7"/>
+      <c r="A134" s="5"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" s="7"/>
+      <c r="A135" s="5"/>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" s="7"/>
+      <c r="A136" s="5"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" s="7"/>
+      <c r="A137" s="5"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" s="7"/>
+      <c r="A138" s="5"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" s="7"/>
+      <c r="A139" s="5"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" s="7"/>
+      <c r="A140" s="5"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" s="7"/>
+      <c r="A141" s="5"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A142" s="7"/>
+      <c r="A142" s="5"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A143" s="7"/>
+      <c r="A143" s="5"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A144" s="7"/>
+      <c r="A144" s="5"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A145" s="7"/>
+      <c r="A145" s="5"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="7"/>
+      <c r="A146" s="5"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A147" s="7"/>
+      <c r="A147" s="5"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A148" s="7"/>
+      <c r="A148" s="5"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" s="7"/>
+      <c r="A149" s="5"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A150" s="7"/>
+      <c r="A150" s="5"/>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A151" s="7"/>
+      <c r="A151" s="5"/>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A152" s="7"/>
+      <c r="A152" s="5"/>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A153" s="7"/>
+      <c r="A153" s="5"/>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A154" s="7"/>
+      <c r="A154" s="5"/>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A155" s="7"/>
+      <c r="A155" s="5"/>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A156" s="7"/>
+      <c r="A156" s="5"/>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A157" s="7"/>
+      <c r="A157" s="5"/>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A158" s="7"/>
+      <c r="A158" s="5"/>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A159" s="7"/>
+      <c r="A159" s="5"/>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A160" s="7"/>
+      <c r="A160" s="5"/>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" s="7"/>
+      <c r="A161" s="5"/>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A162" s="7"/>
+      <c r="A162" s="5"/>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" s="7"/>
+      <c r="A163" s="5"/>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="7"/>
+      <c r="A164" s="5"/>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A165" s="7"/>
+      <c r="A165" s="5"/>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A166" s="7"/>
+      <c r="A166" s="5"/>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A167" s="7"/>
+      <c r="A167" s="5"/>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A168" s="7"/>
+      <c r="A168" s="5"/>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A169" s="7"/>
+      <c r="A169" s="5"/>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A170" s="7"/>
+      <c r="A170" s="5"/>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A171" s="7"/>
+      <c r="A171" s="5"/>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A172" s="7"/>
+      <c r="A172" s="5"/>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A173" s="7"/>
+      <c r="A173" s="5"/>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A174" s="7"/>
+      <c r="A174" s="5"/>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A175" s="7"/>
+      <c r="A175" s="5"/>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A176" s="7"/>
+      <c r="A176" s="5"/>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A177" s="7"/>
+      <c r="A177" s="5"/>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A178" s="7"/>
+      <c r="A178" s="5"/>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A179" s="7"/>
+      <c r="A179" s="5"/>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A180" s="7"/>
+      <c r="A180" s="5"/>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181" s="7"/>
+      <c r="A181" s="5"/>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A182" s="7"/>
+      <c r="A182" s="5"/>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A183" s="7"/>
+      <c r="A183" s="5"/>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A184" s="7"/>
+      <c r="A184" s="5"/>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A185" s="7"/>
+      <c r="A185" s="5"/>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A186" s="7"/>
+      <c r="A186" s="5"/>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A187" s="7"/>
+      <c r="A187" s="5"/>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A188" s="7"/>
+      <c r="A188" s="5"/>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A189" s="7"/>
+      <c r="A189" s="5"/>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A190" s="7"/>
+      <c r="A190" s="5"/>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A191" s="7"/>
+      <c r="A191" s="5"/>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A192" s="7"/>
+      <c r="A192" s="5"/>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A193" s="7"/>
+      <c r="A193" s="5"/>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A194" s="7"/>
+      <c r="A194" s="5"/>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A195" s="7"/>
+      <c r="A195" s="5"/>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A196" s="7"/>
+      <c r="A196" s="5"/>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A197" s="7"/>
+      <c r="A197" s="5"/>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A198" s="7"/>
+      <c r="A198" s="5"/>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A199" s="7"/>
+      <c r="A199" s="5"/>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A200" s="7"/>
+      <c r="A200" s="5"/>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A201" s="7"/>
+      <c r="A201" s="5"/>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A202" s="7"/>
+      <c r="A202" s="5"/>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A203" s="7"/>
+      <c r="A203" s="5"/>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A204" s="7"/>
+      <c r="A204" s="5"/>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A205" s="7"/>
+      <c r="A205" s="5"/>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A206" s="7"/>
+      <c r="A206" s="5"/>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A207" s="7"/>
+      <c r="A207" s="5"/>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A208" s="7"/>
+      <c r="A208" s="5"/>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A209" s="7"/>
+      <c r="A209" s="5"/>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A210" s="7"/>
+      <c r="A210" s="5"/>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A211" s="7"/>
+      <c r="A211" s="5"/>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A212" s="7"/>
+      <c r="A212" s="5"/>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A213" s="7"/>
+      <c r="A213" s="5"/>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A214" s="7"/>
+      <c r="A214" s="5"/>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A215" s="7"/>
+      <c r="A215" s="5"/>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A216" s="7"/>
+      <c r="A216" s="5"/>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A217" s="7"/>
+      <c r="A217" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3545,661 +3358,635 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>128</v>
-      </c>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
+      <c r="A3" s="5"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
+      <c r="A5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
+      <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
+      <c r="A7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
+      <c r="A8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
+      <c r="A9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
+      <c r="A10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
+      <c r="A11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
+      <c r="A13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
+      <c r="A14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
+      <c r="A15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
+      <c r="A17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
+      <c r="A18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
+      <c r="A19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
+      <c r="A20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
+      <c r="A21" s="5"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
+      <c r="A22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
+      <c r="A23" s="5"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
+      <c r="A24" s="5"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
+      <c r="A25" s="5"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
+      <c r="A26" s="5"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
+      <c r="A27" s="5"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
+      <c r="A28" s="5"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
+      <c r="A29" s="5"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
+      <c r="A30" s="5"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
+      <c r="A31" s="5"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
+      <c r="A33" s="5"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
+      <c r="A34" s="5"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
+      <c r="A35" s="5"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
+      <c r="A40" s="5"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
+      <c r="A41" s="5"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
+      <c r="A42" s="5"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
+      <c r="A43" s="5"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
+      <c r="A44" s="5"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
+      <c r="A45" s="5"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
+      <c r="A46" s="5"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
+      <c r="A47" s="5"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
+      <c r="A48" s="5"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
+      <c r="A49" s="5"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
+      <c r="A50" s="5"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
+      <c r="A51" s="5"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
+      <c r="A52" s="5"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="7"/>
+      <c r="A53" s="5"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="7"/>
+      <c r="A54" s="5"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="7"/>
+      <c r="A55" s="5"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="7"/>
+      <c r="A56" s="5"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="7"/>
+      <c r="A57" s="5"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
+      <c r="A58" s="5"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="7"/>
+      <c r="A59" s="5"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
+      <c r="A60" s="5"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
+      <c r="A61" s="5"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="7"/>
+      <c r="A62" s="5"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="7"/>
+      <c r="A63" s="5"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="7"/>
+      <c r="A64" s="5"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="7"/>
+      <c r="A65" s="5"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="7"/>
+      <c r="A66" s="5"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="7"/>
+      <c r="A67" s="5"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="7"/>
+      <c r="A68" s="5"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="7"/>
+      <c r="A69" s="5"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="7"/>
+      <c r="A70" s="5"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="7"/>
+      <c r="A71" s="5"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
+      <c r="A72" s="5"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="7"/>
+      <c r="A73" s="5"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
+      <c r="A74" s="5"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="7"/>
+      <c r="A75" s="5"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="7"/>
+      <c r="A76" s="5"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
+      <c r="A77" s="5"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="7"/>
+      <c r="A78" s="5"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="7"/>
+      <c r="A79" s="5"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="7"/>
+      <c r="A80" s="5"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="7"/>
+      <c r="A81" s="5"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="7"/>
+      <c r="A82" s="5"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="7"/>
+      <c r="A83" s="5"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="7"/>
+      <c r="A84" s="5"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="7"/>
+      <c r="A85" s="5"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="7"/>
+      <c r="A86" s="5"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="7"/>
+      <c r="A87" s="5"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="7"/>
+      <c r="A88" s="5"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="7"/>
+      <c r="A89" s="5"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="7"/>
+      <c r="A90" s="5"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="7"/>
+      <c r="A91" s="5"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="7"/>
+      <c r="A92" s="5"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="7"/>
+      <c r="A93" s="5"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="7"/>
+      <c r="A94" s="5"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="7"/>
+      <c r="A95" s="5"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="7"/>
+      <c r="A96" s="5"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="7"/>
+      <c r="A97" s="5"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="7"/>
+      <c r="A98" s="5"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="7"/>
+      <c r="A99" s="5"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="7"/>
+      <c r="A100" s="5"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="7"/>
+      <c r="A101" s="5"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="7"/>
+      <c r="A102" s="5"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="7"/>
+      <c r="A103" s="5"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="7"/>
+      <c r="A104" s="5"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="7"/>
+      <c r="A105" s="5"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="7"/>
+      <c r="A106" s="5"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="7"/>
+      <c r="A107" s="5"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="7"/>
+      <c r="A108" s="5"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="7"/>
+      <c r="A109" s="5"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="7"/>
+      <c r="A110" s="5"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="7"/>
+      <c r="A111" s="5"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="7"/>
+      <c r="A112" s="5"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="7"/>
+      <c r="A113" s="5"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="7"/>
+      <c r="A114" s="5"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="7"/>
+      <c r="A115" s="5"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="7"/>
+      <c r="A116" s="5"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="7"/>
+      <c r="A117" s="5"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="7"/>
+      <c r="A118" s="5"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="7"/>
+      <c r="A119" s="5"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="7"/>
+      <c r="A120" s="5"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="7"/>
+      <c r="A121" s="5"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="7"/>
+      <c r="A122" s="5"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="7"/>
+      <c r="A123" s="5"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="7"/>
+      <c r="A124" s="5"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="7"/>
+      <c r="A125" s="5"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="7"/>
+      <c r="A126" s="5"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="7"/>
+      <c r="A127" s="5"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="7"/>
+      <c r="A128" s="5"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="7"/>
+      <c r="A129" s="5"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="7"/>
+      <c r="A130" s="5"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="7"/>
+      <c r="A131" s="5"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="7"/>
+      <c r="A132" s="5"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="7"/>
+      <c r="A133" s="5"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="7"/>
+      <c r="A134" s="5"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="7"/>
+      <c r="A135" s="5"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="7"/>
+      <c r="A136" s="5"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="7"/>
+      <c r="A137" s="5"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="7"/>
+      <c r="A138" s="5"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="7"/>
+      <c r="A139" s="5"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="7"/>
+      <c r="A140" s="5"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="7"/>
+      <c r="A141" s="5"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="7"/>
+      <c r="A142" s="5"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="7"/>
+      <c r="A143" s="5"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="7"/>
+      <c r="A144" s="5"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="7"/>
+      <c r="A145" s="5"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="7"/>
+      <c r="A146" s="5"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="7"/>
+      <c r="A147" s="5"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="7"/>
+      <c r="A148" s="5"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="7"/>
+      <c r="A149" s="5"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="7"/>
+      <c r="A150" s="5"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="7"/>
+      <c r="A151" s="5"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="7"/>
+      <c r="A152" s="5"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="7"/>
+      <c r="A153" s="5"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="7"/>
+      <c r="A154" s="5"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="7"/>
+      <c r="A155" s="5"/>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="7"/>
+      <c r="A156" s="5"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="7"/>
+      <c r="A157" s="5"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="7"/>
+      <c r="A158" s="5"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="7"/>
+      <c r="A159" s="5"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="7"/>
+      <c r="A160" s="5"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="7"/>
+      <c r="A161" s="5"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="7"/>
+      <c r="A162" s="5"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="7"/>
+      <c r="A163" s="5"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" s="7"/>
+      <c r="A164" s="5"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="7"/>
+      <c r="A165" s="5"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="7"/>
+      <c r="A166" s="5"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="7"/>
+      <c r="A167" s="5"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="7"/>
+      <c r="A168" s="5"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" s="7"/>
+      <c r="A169" s="5"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="7"/>
+      <c r="A170" s="5"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="7"/>
+      <c r="A171" s="5"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="7"/>
+      <c r="A172" s="5"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" s="7"/>
+      <c r="A173" s="5"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="7"/>
+      <c r="A174" s="5"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="7"/>
+      <c r="A175" s="5"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="7"/>
+      <c r="A176" s="5"/>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="7"/>
+      <c r="A177" s="5"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" s="7"/>
+      <c r="A178" s="5"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" s="7"/>
+      <c r="A179" s="5"/>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="7"/>
+      <c r="A180" s="5"/>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A181" s="7"/>
+      <c r="A181" s="5"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A182" s="7"/>
+      <c r="A182" s="5"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="7"/>
+      <c r="A183" s="5"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="7"/>
+      <c r="A184" s="5"/>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="7"/>
+      <c r="A185" s="5"/>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="7"/>
+      <c r="A186" s="5"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="7"/>
+      <c r="A187" s="5"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="7"/>
+      <c r="A188" s="5"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="7"/>
+      <c r="A189" s="5"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="7"/>
+      <c r="A190" s="5"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="7"/>
+      <c r="A191" s="5"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="7"/>
+      <c r="A192" s="5"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="7"/>
+      <c r="A193" s="5"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="7"/>
+      <c r="A194" s="5"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="7"/>
+      <c r="A195" s="5"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="7"/>
+      <c r="A196" s="5"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="7"/>
+      <c r="A197" s="5"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A198" s="7"/>
+      <c r="A198" s="5"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="7"/>
+      <c r="A199" s="5"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A200" s="7"/>
+      <c r="A200" s="5"/>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A201" s="7"/>
+      <c r="A201" s="5"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="7"/>
+      <c r="A202" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="14">
@@ -4271,655 +4058,632 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>137</v>
-      </c>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
+      <c r="A3" s="5"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
+      <c r="A5" s="5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
+      <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
+      <c r="A7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
+      <c r="A8" s="5"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
+      <c r="A9" s="5"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
+      <c r="A10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
+      <c r="A11" s="5"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
+      <c r="A13" s="5"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
+      <c r="A14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
+      <c r="A15" s="5"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
+      <c r="A17" s="5"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
+      <c r="A18" s="5"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
+      <c r="A19" s="5"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
+      <c r="A20" s="5"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
+      <c r="A21" s="5"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
+      <c r="A22" s="5"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
+      <c r="A23" s="5"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
+      <c r="A24" s="5"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
+      <c r="A25" s="5"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
+      <c r="A26" s="5"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
+      <c r="A27" s="5"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
+      <c r="A28" s="5"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
+      <c r="A29" s="5"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
+      <c r="A30" s="5"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
+      <c r="A31" s="5"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
+      <c r="A33" s="5"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
+      <c r="A34" s="5"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
+      <c r="A35" s="5"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
+      <c r="A40" s="5"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
+      <c r="A41" s="5"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
+      <c r="A42" s="5"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
+      <c r="A43" s="5"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
+      <c r="A44" s="5"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
+      <c r="A45" s="5"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
+      <c r="A46" s="5"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
+      <c r="A47" s="5"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
+      <c r="A48" s="5"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
+      <c r="A49" s="5"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
+      <c r="A50" s="5"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
+      <c r="A51" s="5"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
+      <c r="A52" s="5"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="7"/>
+      <c r="A53" s="5"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="7"/>
+      <c r="A54" s="5"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="7"/>
+      <c r="A55" s="5"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="7"/>
+      <c r="A56" s="5"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="7"/>
+      <c r="A57" s="5"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
+      <c r="A58" s="5"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="7"/>
+      <c r="A59" s="5"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
+      <c r="A60" s="5"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
+      <c r="A61" s="5"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="7"/>
+      <c r="A62" s="5"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="7"/>
+      <c r="A63" s="5"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="7"/>
+      <c r="A64" s="5"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="7"/>
+      <c r="A65" s="5"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="7"/>
+      <c r="A66" s="5"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="7"/>
+      <c r="A67" s="5"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="7"/>
+      <c r="A68" s="5"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="7"/>
+      <c r="A69" s="5"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="7"/>
+      <c r="A70" s="5"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="7"/>
+      <c r="A71" s="5"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
+      <c r="A72" s="5"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="7"/>
+      <c r="A73" s="5"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
+      <c r="A74" s="5"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="7"/>
+      <c r="A75" s="5"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="7"/>
+      <c r="A76" s="5"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
+      <c r="A77" s="5"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="7"/>
+      <c r="A78" s="5"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="7"/>
+      <c r="A79" s="5"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="7"/>
+      <c r="A80" s="5"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="7"/>
+      <c r="A81" s="5"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="7"/>
+      <c r="A82" s="5"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="7"/>
+      <c r="A83" s="5"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="7"/>
+      <c r="A84" s="5"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="7"/>
+      <c r="A85" s="5"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="7"/>
+      <c r="A86" s="5"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="7"/>
+      <c r="A87" s="5"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="7"/>
+      <c r="A88" s="5"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="7"/>
+      <c r="A89" s="5"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="7"/>
+      <c r="A90" s="5"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="7"/>
+      <c r="A91" s="5"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="7"/>
+      <c r="A92" s="5"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="7"/>
+      <c r="A93" s="5"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="7"/>
+      <c r="A94" s="5"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="7"/>
+      <c r="A95" s="5"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="7"/>
+      <c r="A96" s="5"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="7"/>
+      <c r="A97" s="5"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="7"/>
+      <c r="A98" s="5"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="7"/>
+      <c r="A99" s="5"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="7"/>
+      <c r="A100" s="5"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="7"/>
+      <c r="A101" s="5"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="7"/>
+      <c r="A102" s="5"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="7"/>
+      <c r="A103" s="5"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="7"/>
+      <c r="A104" s="5"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="7"/>
+      <c r="A105" s="5"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="7"/>
+      <c r="A106" s="5"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="7"/>
+      <c r="A107" s="5"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="7"/>
+      <c r="A108" s="5"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="7"/>
+      <c r="A109" s="5"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="7"/>
+      <c r="A110" s="5"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="7"/>
+      <c r="A111" s="5"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="7"/>
+      <c r="A112" s="5"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="7"/>
+      <c r="A113" s="5"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="7"/>
+      <c r="A114" s="5"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="7"/>
+      <c r="A115" s="5"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="7"/>
+      <c r="A116" s="5"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="7"/>
+      <c r="A117" s="5"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="7"/>
+      <c r="A118" s="5"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="7"/>
+      <c r="A119" s="5"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="7"/>
+      <c r="A120" s="5"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="7"/>
+      <c r="A121" s="5"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="7"/>
+      <c r="A122" s="5"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="7"/>
+      <c r="A123" s="5"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="7"/>
+      <c r="A124" s="5"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="7"/>
+      <c r="A125" s="5"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="7"/>
+      <c r="A126" s="5"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="7"/>
+      <c r="A127" s="5"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="7"/>
+      <c r="A128" s="5"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="7"/>
+      <c r="A129" s="5"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="7"/>
+      <c r="A130" s="5"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="7"/>
+      <c r="A131" s="5"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="7"/>
+      <c r="A132" s="5"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="7"/>
+      <c r="A133" s="5"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="7"/>
+      <c r="A134" s="5"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="7"/>
+      <c r="A135" s="5"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="7"/>
+      <c r="A136" s="5"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="7"/>
+      <c r="A137" s="5"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="7"/>
+      <c r="A138" s="5"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="7"/>
+      <c r="A139" s="5"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="7"/>
+      <c r="A140" s="5"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="7"/>
+      <c r="A141" s="5"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" s="7"/>
+      <c r="A142" s="5"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" s="7"/>
+      <c r="A143" s="5"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="7"/>
+      <c r="A144" s="5"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="7"/>
+      <c r="A145" s="5"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="7"/>
+      <c r="A146" s="5"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="7"/>
+      <c r="A147" s="5"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="7"/>
+      <c r="A148" s="5"/>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" s="7"/>
+      <c r="A149" s="5"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" s="7"/>
+      <c r="A150" s="5"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="7"/>
+      <c r="A151" s="5"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="7"/>
+      <c r="A152" s="5"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="7"/>
+      <c r="A153" s="5"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="7"/>
+      <c r="A154" s="5"/>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155" s="7"/>
+      <c r="A155" s="5"/>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="7"/>
+      <c r="A156" s="5"/>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="7"/>
+      <c r="A157" s="5"/>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" s="7"/>
+      <c r="A158" s="5"/>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" s="7"/>
+      <c r="A159" s="5"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="7"/>
+      <c r="A160" s="5"/>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="7"/>
+      <c r="A161" s="5"/>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A162" s="7"/>
+      <c r="A162" s="5"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163" s="7"/>
+      <c r="A163" s="5"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164" s="7"/>
+      <c r="A164" s="5"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A165" s="7"/>
+      <c r="A165" s="5"/>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="7"/>
+      <c r="A166" s="5"/>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A167" s="7"/>
+      <c r="A167" s="5"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A168" s="7"/>
+      <c r="A168" s="5"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A169" s="7"/>
+      <c r="A169" s="5"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="7"/>
+      <c r="A170" s="5"/>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171" s="7"/>
+      <c r="A171" s="5"/>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A172" s="7"/>
+      <c r="A172" s="5"/>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A173" s="7"/>
+      <c r="A173" s="5"/>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A174" s="7"/>
+      <c r="A174" s="5"/>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" s="7"/>
+      <c r="A175" s="5"/>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A176" s="7"/>
+      <c r="A176" s="5"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" s="7"/>
+      <c r="A177" s="5"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" s="7"/>
+      <c r="A178" s="5"/>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="7"/>
+      <c r="A179" s="5"/>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A180" s="7"/>
+      <c r="A180" s="5"/>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A181" s="7"/>
+      <c r="A181" s="5"/>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A182" s="7"/>
+      <c r="A182" s="5"/>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183" s="7"/>
+      <c r="A183" s="5"/>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A184" s="7"/>
+      <c r="A184" s="5"/>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="7"/>
+      <c r="A185" s="5"/>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" s="7"/>
+      <c r="A186" s="5"/>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A187" s="7"/>
+      <c r="A187" s="5"/>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A188" s="7"/>
+      <c r="A188" s="5"/>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A189" s="7"/>
+      <c r="A189" s="5"/>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A190" s="7"/>
+      <c r="A190" s="5"/>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A191" s="7"/>
+      <c r="A191" s="5"/>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A192" s="7"/>
+      <c r="A192" s="5"/>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A193" s="7"/>
+      <c r="A193" s="5"/>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A194" s="7"/>
+      <c r="A194" s="5"/>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A195" s="7"/>
+      <c r="A195" s="5"/>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A196" s="7"/>
+      <c r="A196" s="5"/>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A197" s="7"/>
+      <c r="A197" s="5"/>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A198" s="7"/>
+      <c r="A198" s="5"/>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A199" s="7"/>
+      <c r="A199" s="5"/>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A200" s="7"/>
+      <c r="A200" s="5"/>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A201" s="7"/>
+      <c r="A201" s="5"/>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A202" s="7"/>
+      <c r="A202" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="12">
@@ -4982,637 +4746,623 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>142</v>
-      </c>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
+      <c r="A3" s="5"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
+      <c r="A5" s="5"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
+      <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
+      <c r="A7" s="5"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
+      <c r="A8" s="5"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
+      <c r="A9" s="5"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
+      <c r="A10" s="5"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
+      <c r="A11" s="5"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
+      <c r="A13" s="5"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
+      <c r="A14" s="5"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
+      <c r="A15" s="5"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
+      <c r="A17" s="5"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
+      <c r="A18" s="5"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
+      <c r="A19" s="5"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
+      <c r="A20" s="5"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
+      <c r="A21" s="5"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
+      <c r="A22" s="5"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
+      <c r="A23" s="5"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
+      <c r="A24" s="5"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
+      <c r="A25" s="5"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
+      <c r="A26" s="5"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
+      <c r="A27" s="5"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
+      <c r="A28" s="5"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
+      <c r="A29" s="5"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
+      <c r="A30" s="5"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
+      <c r="A31" s="5"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
+      <c r="A33" s="5"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
+      <c r="A34" s="5"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
+      <c r="A35" s="5"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
+      <c r="A40" s="5"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
+      <c r="A41" s="5"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
+      <c r="A42" s="5"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
+      <c r="A43" s="5"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
+      <c r="A44" s="5"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
+      <c r="A45" s="5"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
+      <c r="A46" s="5"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
+      <c r="A47" s="5"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
+      <c r="A48" s="5"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
+      <c r="A49" s="5"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
+      <c r="A50" s="5"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
+      <c r="A51" s="5"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
+      <c r="A52" s="5"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="7"/>
+      <c r="A53" s="5"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="7"/>
+      <c r="A54" s="5"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="7"/>
+      <c r="A55" s="5"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="7"/>
+      <c r="A56" s="5"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="7"/>
+      <c r="A57" s="5"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
+      <c r="A58" s="5"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="7"/>
+      <c r="A59" s="5"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
+      <c r="A60" s="5"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
+      <c r="A61" s="5"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="7"/>
+      <c r="A62" s="5"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="7"/>
+      <c r="A63" s="5"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="7"/>
+      <c r="A64" s="5"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="7"/>
+      <c r="A65" s="5"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="7"/>
+      <c r="A66" s="5"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="7"/>
+      <c r="A67" s="5"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="7"/>
+      <c r="A68" s="5"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="7"/>
+      <c r="A69" s="5"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="7"/>
+      <c r="A70" s="5"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="7"/>
+      <c r="A71" s="5"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
+      <c r="A72" s="5"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="7"/>
+      <c r="A73" s="5"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
+      <c r="A74" s="5"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="7"/>
+      <c r="A75" s="5"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="7"/>
+      <c r="A76" s="5"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
+      <c r="A77" s="5"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="7"/>
+      <c r="A78" s="5"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="7"/>
+      <c r="A79" s="5"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="7"/>
+      <c r="A80" s="5"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="7"/>
+      <c r="A81" s="5"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="7"/>
+      <c r="A82" s="5"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="7"/>
+      <c r="A83" s="5"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="7"/>
+      <c r="A84" s="5"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="7"/>
+      <c r="A85" s="5"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="7"/>
+      <c r="A86" s="5"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="7"/>
+      <c r="A87" s="5"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="7"/>
+      <c r="A88" s="5"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="7"/>
+      <c r="A89" s="5"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="7"/>
+      <c r="A90" s="5"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="7"/>
+      <c r="A91" s="5"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="7"/>
+      <c r="A92" s="5"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="7"/>
+      <c r="A93" s="5"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="7"/>
+      <c r="A94" s="5"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="7"/>
+      <c r="A95" s="5"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="7"/>
+      <c r="A96" s="5"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="7"/>
+      <c r="A97" s="5"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="7"/>
+      <c r="A98" s="5"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="7"/>
+      <c r="A99" s="5"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="7"/>
+      <c r="A100" s="5"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="7"/>
+      <c r="A101" s="5"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="7"/>
+      <c r="A102" s="5"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="7"/>
+      <c r="A103" s="5"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="7"/>
+      <c r="A104" s="5"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="7"/>
+      <c r="A105" s="5"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="7"/>
+      <c r="A106" s="5"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="7"/>
+      <c r="A107" s="5"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="7"/>
+      <c r="A108" s="5"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="7"/>
+      <c r="A109" s="5"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="7"/>
+      <c r="A110" s="5"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="7"/>
+      <c r="A111" s="5"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="7"/>
+      <c r="A112" s="5"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="7"/>
+      <c r="A113" s="5"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="7"/>
+      <c r="A114" s="5"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="7"/>
+      <c r="A115" s="5"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="7"/>
+      <c r="A116" s="5"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="7"/>
+      <c r="A117" s="5"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="7"/>
+      <c r="A118" s="5"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="7"/>
+      <c r="A119" s="5"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="7"/>
+      <c r="A120" s="5"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="7"/>
+      <c r="A121" s="5"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="7"/>
+      <c r="A122" s="5"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="7"/>
+      <c r="A123" s="5"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="7"/>
+      <c r="A124" s="5"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="7"/>
+      <c r="A125" s="5"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="7"/>
+      <c r="A126" s="5"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="7"/>
+      <c r="A127" s="5"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="7"/>
+      <c r="A128" s="5"/>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="7"/>
+      <c r="A129" s="5"/>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="7"/>
+      <c r="A130" s="5"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="7"/>
+      <c r="A131" s="5"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="7"/>
+      <c r="A132" s="5"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="7"/>
+      <c r="A133" s="5"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="7"/>
+      <c r="A134" s="5"/>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="7"/>
+      <c r="A135" s="5"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="7"/>
+      <c r="A136" s="5"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="7"/>
+      <c r="A137" s="5"/>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="7"/>
+      <c r="A138" s="5"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="7"/>
+      <c r="A139" s="5"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="7"/>
+      <c r="A140" s="5"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="7"/>
+      <c r="A141" s="5"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="7"/>
+      <c r="A142" s="5"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="7"/>
+      <c r="A143" s="5"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" s="7"/>
+      <c r="A144" s="5"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" s="7"/>
+      <c r="A145" s="5"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" s="7"/>
+      <c r="A146" s="5"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" s="7"/>
+      <c r="A147" s="5"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148" s="7"/>
+      <c r="A148" s="5"/>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" s="7"/>
+      <c r="A149" s="5"/>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" s="7"/>
+      <c r="A150" s="5"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" s="7"/>
+      <c r="A151" s="5"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A152" s="7"/>
+      <c r="A152" s="5"/>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A153" s="7"/>
+      <c r="A153" s="5"/>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" s="7"/>
+      <c r="A154" s="5"/>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" s="7"/>
+      <c r="A155" s="5"/>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" s="7"/>
+      <c r="A156" s="5"/>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" s="7"/>
+      <c r="A157" s="5"/>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" s="7"/>
+      <c r="A158" s="5"/>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" s="7"/>
+      <c r="A159" s="5"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" s="7"/>
+      <c r="A160" s="5"/>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="7"/>
+      <c r="A161" s="5"/>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="7"/>
+      <c r="A162" s="5"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" s="7"/>
+      <c r="A163" s="5"/>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" s="7"/>
+      <c r="A164" s="5"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" s="7"/>
+      <c r="A165" s="5"/>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="7"/>
+      <c r="A166" s="5"/>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" s="7"/>
+      <c r="A167" s="5"/>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="7"/>
+      <c r="A168" s="5"/>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" s="7"/>
+      <c r="A169" s="5"/>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="7"/>
+      <c r="A170" s="5"/>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="7"/>
+      <c r="A171" s="5"/>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="7"/>
+      <c r="A172" s="5"/>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" s="7"/>
+      <c r="A173" s="5"/>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="7"/>
+      <c r="A174" s="5"/>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="7"/>
+      <c r="A175" s="5"/>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="7"/>
+      <c r="A176" s="5"/>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="7"/>
+      <c r="A177" s="5"/>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" s="7"/>
+      <c r="A178" s="5"/>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="7"/>
+      <c r="A179" s="5"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="7"/>
+      <c r="A180" s="5"/>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="7"/>
+      <c r="A181" s="5"/>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" s="7"/>
+      <c r="A182" s="5"/>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="7"/>
+      <c r="A183" s="5"/>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="7"/>
+      <c r="A184" s="5"/>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" s="7"/>
+      <c r="A185" s="5"/>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="7"/>
+      <c r="A186" s="5"/>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" s="7"/>
+      <c r="A187" s="5"/>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="7"/>
+      <c r="A188" s="5"/>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="7"/>
+      <c r="A189" s="5"/>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="7"/>
+      <c r="A190" s="5"/>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" s="7"/>
+      <c r="A191" s="5"/>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="7"/>
+      <c r="A192" s="5"/>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A193" s="7"/>
+      <c r="A193" s="5"/>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A194" s="7"/>
+      <c r="A194" s="5"/>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" s="7"/>
+      <c r="A195" s="5"/>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A196" s="7"/>
+      <c r="A196" s="5"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" s="7"/>
+      <c r="A197" s="5"/>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" s="7"/>
+      <c r="A198" s="5"/>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" s="7"/>
+      <c r="A199" s="5"/>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A200" s="7"/>
+      <c r="A200" s="5"/>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A201" s="7"/>
+      <c r="A201" s="5"/>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A202" s="7"/>
+      <c r="A202" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="6">

--- a/scripts/ground-truth/_template.xlsx
+++ b/scripts/ground-truth/_template.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="110">
   <si>
     <t>STIX Match Ground-Truth Tagger</t>
   </si>
@@ -74,7 +74,13 @@
     <t xml:space="preserve"> • Dropdowns appear as you click into a cell — pick from the list rather than typing free text.</t>
   </si>
   <si>
-    <t xml:space="preserve"> • If you are unsure of a field, leave it blank. The converter handles missing values cleanly.</t>
+    <t xml:space="preserve"> • Keeper team — pick "Us" if the event is for the analyzed GK (the paying customer). Pick "Opponent" if the event is for the OTHER GK. Tag BOTH GKs' events — opponent events are pure training signal for the model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> • GK substitution — if either team subbed their GK, enter the MM:SS timestamp on the Metadata sheet ("Us GK sub at" / "Opponent GK sub at"). The converter tags every event before that time as keeper_slot=1 and every event after as keeper_slot=2. Leave blank if same GK all game.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> • If you are unsure of a field, leave it blank. The converter handles missing values cleanly. Blank Keeper team defaults to "Us".</t>
   </si>
   <si>
     <t xml:space="preserve"> • Notes are always optional but valuable — they become part of the match record on publish.</t>
@@ -86,22 +92,22 @@
     <t>FORMAT EXAMPLES (copy the IDEA, not the literal row, into the relevant sheet):</t>
   </si>
   <si>
-    <t xml:space="preserve">  Goals: 4:05 | 1 | Us | Open play | Rebound | 6-Yard Box | Low | Centre | Right-side initial shot saved, follow-up tap-in central. | Opp GK was on ground from initial save. | (notes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Saves: 24:47 | 1 | Central Distance | Foot | Yes | Parry | Yes | Corner | C | Low | GK Right | Driven shot from outside the box, central. | Strong parry — full extension dive to the right. | (notes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Distribution: 14:32 | 1 | Backpass | Pass | Yes | Yes | Switch wide | Left | Defender | Clean | Recycled possession to LCB under high press.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Crosses: 36:18 | 2 | Corner Right | Whipped | Near post | Punch | Edge of 6yd | Punched away | Two-fisted punch under pressure from two attackers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Sweeper: 28:15 | 1 | Clearance | 5–15 yards out | Yes | 1 attacker | Cleared safely | Read the through ball early.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1v1s: 52:17 | 2 | 1v1 faced | Conceded | Through ball over the top, GK rushed off line, attacker rounded him.</t>
+    <t xml:space="preserve">  Goals: 4:05 | 1 | Opponent | Us | Open play | Rebound | 6-Yard Box | Low | Centre | Right-side initial shot saved, follow-up tap-in central. | Opp GK was on ground from initial save. | (notes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Saves: 24:47 | 1 | Us | Central Distance | Foot | Yes | Parry | Yes | Corner | C | Low | GK Right | Driven shot from outside the box, central. | Strong parry — full extension dive to the right. | (notes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Distribution: 14:32 | 1 | Us | Backpass | Pass | Yes | Yes | Switch wide | Left | Defender | Clean | Recycled possession to LCB under high press.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Crosses: 36:18 | 2 | Us | Corner Right | Whipped | Near post | Punch | Edge of 6yd | Punched away | Two-fisted punch under pressure from two attackers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Sweeper: 28:15 | 1 | Us | Clearance | 5–15 yards out | Yes | 1 attacker | Cleared safely | Read the through ball early.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1v1s: 52:17 | 2 | Us | 1v1 faced | Conceded | Through ball over the top, GK rushed off line, attacker rounded him.</t>
   </si>
   <si>
     <t>Field</t>
@@ -191,6 +197,18 @@
     <t>Final score — them</t>
   </si>
   <si>
+    <t>Us GK sub at (MM:SS)</t>
+  </si>
+  <si>
+    <t>Leave blank if same GK all game. Otherwise MM:SS when your GK was subbed. Events after this time attribute to GK 2.</t>
+  </si>
+  <si>
+    <t>Opponent GK sub at (MM:SS)</t>
+  </si>
+  <si>
+    <t>Leave blank if same opponent GK all game. Otherwise MM:SS when the opposition GK was subbed.</t>
+  </si>
+  <si>
     <t>video_job_id</t>
   </si>
   <si>
@@ -201,6 +219,9 @@
   </si>
   <si>
     <t>Half</t>
+  </si>
+  <si>
+    <t>Keeper team</t>
   </si>
   <si>
     <t>Scoring team</t>
@@ -746,7 +767,7 @@
   <sheetPr>
     <tabColor rgb="FF888888"/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -859,12 +880,12 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>20</v>
+      <c r="A23" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -873,8 +894,8 @@
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>21</v>
+      <c r="A25" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -884,12 +905,12 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -910,6 +931,16 @@
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +954,7 @@
   <sheetPr>
     <tabColor rgb="FF666666"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -933,110 +964,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B12">
         <v>4</v>
@@ -1044,7 +1075,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1052,13 +1083,35 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1083,655 +1136,658 @@
   <sheetPr>
     <tabColor rgb="FFEF4444"/>
   </sheetPr>
-  <dimension ref="A1:K202"/>
+  <dimension ref="A1:L202"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="8" width="16" customWidth="1"/>
-    <col min="9" max="10" width="50" customWidth="1"/>
-    <col min="11" max="11" width="40" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="9" width="16" customWidth="1"/>
+    <col min="10" max="11" width="50" customWidth="1"/>
+    <col min="12" max="12" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
   </sheetData>
@@ -1742,40 +1798,40 @@
     <dataValidation type="list" allowBlank="1" sqref="B2:B202">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C10:C202">
+    <dataValidation type="list" allowBlank="1" sqref="C10:D202">
       <formula1>"Us,Opponent"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+    <dataValidation type="list" allowBlank="1" sqref="C2:D202">
       <formula1>"Us,Opponent"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
+    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
       <formula1>"Open play,Counter attack,Corner,Free kick,Penalty,Throw-in,Set piece other,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
       <formula1>"Open play,Counter attack,Corner,Free kick,Penalty,Throw-in,Set piece other,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
+    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
       <formula1>"Header,Driven,Tap-in,Volley,Half-volley,Curled,Chip,One-v-one finish,Rebound,Deflection,Penalty,Free-kick,Own goal,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
       <formula1>"Header,Driven,Tap-in,Volley,Half-volley,Curled,Chip,One-v-one finish,Rebound,Deflection,Penalty,Free-kick,Own goal,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
+    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
       <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
       <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
+    <dataValidation type="list" allowBlank="1" sqref="H10:H202">
       <formula1>"Top,Mid,Low,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H202">
       <formula1>"Top,Mid,Low,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H10:H202">
+    <dataValidation type="list" allowBlank="1" sqref="I10:I202">
       <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H202">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I202">
       <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1789,671 +1845,675 @@
   <sheetPr>
     <tabColor rgb="FF10B981"/>
   </sheetPr>
-  <dimension ref="A1:N202"/>
+  <dimension ref="A1:O202"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="11" width="16" customWidth="1"/>
-    <col min="12" max="13" width="50" customWidth="1"/>
-    <col min="14" max="14" width="40" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="12" width="16" customWidth="1"/>
+    <col min="13" max="14" width="50" customWidth="1"/>
+    <col min="15" max="15" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>70</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="N1" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="20">
+  <dataValidations count="22">
     <dataValidation type="list" allowBlank="1" sqref="B10:B202">
       <formula1>"1,2"</formula1>
     </dataValidation>
@@ -2461,57 +2521,63 @@
       <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C10:C202">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
       <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
       <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
+    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
       <formula1>"Foot,Header,Deflection"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
       <formula1>"Foot,Header,Deflection"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
+    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
       <formula1>"Yes,No,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
       <formula1>"Yes,No,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
+    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
       <formula1>"Catch,Block,Parry,Deflect,Punch,Smother,Starfish,K-Barrier,Missed,Goal,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
       <formula1>"Catch,Block,Parry,Deflect,Punch,Smother,Starfish,K-Barrier,Missed,Goal,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
+    <dataValidation type="list" allowBlank="1" sqref="H10:H202">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H202">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H10:H202">
+    <dataValidation type="list" allowBlank="1" sqref="I10:I202">
       <formula1>"Held,Rebound (safe),Rebound (dangerous),Corner,Out of play,Goal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H202">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I202">
       <formula1>"Held,Rebound (safe),Rebound (dangerous),Corner,Out of play,Goal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I10:I202">
+    <dataValidation type="list" allowBlank="1" sqref="J10:J202">
       <formula1>"A,B,C,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I202">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J202">
       <formula1>"A,B,C,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J10:J202">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K202">
       <formula1>"Top,Mid,Low,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J202">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K202">
       <formula1>"Top,Mid,Low,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K10:K202">
+    <dataValidation type="list" allowBlank="1" sqref="L10:L202">
       <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K202">
+    <dataValidation type="list" allowBlank="1" sqref="L2:L202">
       <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2525,25 +2591,26 @@
   <sheetPr>
     <tabColor rgb="FF3B82F6"/>
   </sheetPr>
-  <dimension ref="A1:K217"/>
+  <dimension ref="A1:L217"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="40" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2553,7 +2620,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2563,7 +2630,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -2571,7 +2638,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -2579,7 +2646,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -2587,7 +2654,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -2595,7 +2662,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
@@ -2603,7 +2670,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -2611,7 +2678,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
@@ -2619,7 +2686,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
@@ -2627,7 +2694,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2635,648 +2702,651 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="5"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="5"/>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="5"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="5"/>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="5"/>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="5"/>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="5"/>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="5"/>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="5"/>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="5"/>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="5"/>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="5"/>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="5"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="5"/>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="5"/>
     </row>
   </sheetData>
@@ -3284,7 +3354,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <dataValidations count="16">
+  <dataValidations count="18">
     <dataValidation type="list" allowBlank="1" sqref="B100:B217">
       <formula1>"1,2"</formula1>
     </dataValidation>
@@ -3292,45 +3362,51 @@
       <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C100:C217">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C17:C217">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D100:D217">
       <formula1>"Goal kick,After save,Backpass,Loose ball in box,Throw-in to GK,Free kick to GK"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C17:C217">
+    <dataValidation type="list" allowBlank="1" sqref="D17:D217">
       <formula1>"Goal kick,After save,Backpass,Loose ball in box,Throw-in to GK,Free kick to GK"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D100:D217">
+    <dataValidation type="list" allowBlank="1" sqref="E100:E217">
       <formula1>"GK Short Kick,GK Long Kick,Throw,Pass,Drop-kick"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D17:D217">
+    <dataValidation type="list" allowBlank="1" sqref="E17:E217">
       <formula1>"GK Short Kick,GK Long Kick,Throw,Pass,Drop-kick"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E100:F217">
+    <dataValidation type="list" allowBlank="1" sqref="F100:G217">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E17:F217">
+    <dataValidation type="list" allowBlank="1" sqref="F17:G217">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G100:G217">
+    <dataValidation type="list" allowBlank="1" sqref="H100:H217">
       <formula1>"Short to defender,Sideways across back,Long to forward,Switch wide,Backwards under pressure,Clearance under pressure,Drilled into channel"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G17:G217">
+    <dataValidation type="list" allowBlank="1" sqref="H17:H217">
       <formula1>"Short to defender,Sideways across back,Long to forward,Switch wide,Backwards under pressure,Clearance under pressure,Drilled into channel"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H100:H217">
+    <dataValidation type="list" allowBlank="1" sqref="I100:I217">
       <formula1>"Left,Centre,Right,Backwards"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H17:H217">
+    <dataValidation type="list" allowBlank="1" sqref="I17:I217">
       <formula1>"Left,Centre,Right,Backwards"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I100:I217">
+    <dataValidation type="list" allowBlank="1" sqref="J100:J217">
       <formula1>"Defender,Midfielder,Forward,Out of play,Opponent (turnover)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I17:I217">
+    <dataValidation type="list" allowBlank="1" sqref="J17:J217">
       <formula1>"Defender,Midfielder,Forward,Out of play,Opponent (turnover)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J100:J217">
+    <dataValidation type="list" allowBlank="1" sqref="K100:K217">
       <formula1>"Clean,Heavy,Two touches,Mishit"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J17:J217">
+    <dataValidation type="list" allowBlank="1" sqref="K17:K217">
       <formula1>"Clean,Heavy,Two touches,Mishit"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3344,652 +3420,655 @@
   <sheetPr>
     <tabColor rgb="FFF97316"/>
   </sheetPr>
-  <dimension ref="A1:I202"/>
+  <dimension ref="A1:J202"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="3" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="14">
+  <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" sqref="B10:B202">
       <formula1>"1,2"</formula1>
     </dataValidation>
@@ -3997,39 +4076,45 @@
       <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C10:C202">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
       <formula1>"Left,Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
       <formula1>"Left,Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
+    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
       <formula1>"Whipped,Floated,Driven,Cut-back,Looped"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
       <formula1>"Whipped,Floated,Driven,Cut-back,Looped"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
+    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
       <formula1>"Near post,6yd,Penalty spot,Far post,Out of box"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
       <formula1>"Near post,6yd,Penalty spot,Far post,Out of box"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
+    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
       <formula1>"Catch,Punch,Tip-over,Stayed on line,Missed/Misjudged,Defender cleared"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
       <formula1>"Catch,Punch,Tip-over,Stayed on line,Missed/Misjudged,Defender cleared"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
+    <dataValidation type="list" allowBlank="1" sqref="H10:H202">
       <formula1>"On line,Edge of 6yd,Edge of 18yd,Outside box"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H202">
       <formula1>"On line,Edge of 6yd,Edge of 18yd,Outside box"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H10:H202">
+    <dataValidation type="list" allowBlank="1" sqref="I10:I202">
       <formula1>"Held,Punched away,Tipped over,Conceded,Cleared by defender,Shot from rebound"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H202">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I202">
       <formula1>"Held,Punched away,Tipped over,Conceded,Cleared by defender,Shot from rebound"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4043,650 +4128,653 @@
   <sheetPr>
     <tabColor rgb="FFA78BFA"/>
   </sheetPr>
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:I202"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="14">
     <dataValidation type="list" allowBlank="1" sqref="B10:B202">
       <formula1>"1,2"</formula1>
     </dataValidation>
@@ -4694,33 +4782,39 @@
       <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C10:C202">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
       <formula1>"Clearance,Interception,Tackle,Header"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
       <formula1>"Clearance,Interception,Tackle,Header"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
+    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
       <formula1>"In box,Edge of box,5–15 yards out,15+ yards out"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
       <formula1>"In box,Edge of box,5–15 yards out,15+ yards out"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
+    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
+    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
       <formula1>"None,1 attacker,2+ attackers"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
       <formula1>"None,1 attacker,2+ attackers"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
+    <dataValidation type="list" allowBlank="1" sqref="H10:H202">
       <formula1>"Possession retained,Cleared safely,Conceded turnover,Goal conceded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H202">
       <formula1>"Possession retained,Cleared safely,Conceded turnover,Goal conceded"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4734,638 +4828,642 @@
   <sheetPr>
     <tabColor rgb="FFD4A853"/>
   </sheetPr>
-  <dimension ref="A1:E202"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="70" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" sqref="B10:B202">
       <formula1>"1,2"</formula1>
     </dataValidation>
@@ -5373,15 +5471,21 @@
       <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C10:C202">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
       <formula1>"1v1 faced,Recovery save,Error leading to goal,Big moment (other)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
       <formula1>"1v1 faced,Recovery save,Error leading to goal,Big moment (other)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
+    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
       <formula1>"Won,Conceded,Saved,Cleared"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
       <formula1>"Won,Conceded,Saved,Cleared"</formula1>
     </dataValidation>
   </dataValidations>

--- a/scripts/ground-truth/_template.xlsx
+++ b/scripts/ground-truth/_template.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="108">
   <si>
     <t>STIX Match Ground-Truth Tagger</t>
   </si>
@@ -122,79 +122,73 @@
     <t>Match name</t>
   </si>
   <si>
-    <t>judah-vs-ofc-2026-04-25</t>
-  </si>
-  <si>
-    <t>Short slug for the match (used as filename and id)</t>
+    <t>Short slug for the match (used as filename and id) — e.g. judah-vs-ofc-2026-04-25</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
+    <t>YYYY-MM-DD — e.g. 2026-04-25</t>
   </si>
   <si>
     <t>Opponent</t>
   </si>
   <si>
-    <t>OFC 2016</t>
-  </si>
-  <si>
-    <t>Opposition team name</t>
+    <t>Opposition team name — e.g. OFC 2016</t>
   </si>
   <si>
     <t>Venue</t>
   </si>
   <si>
-    <t>Home</t>
+    <t>e.g. Home</t>
   </si>
   <si>
     <t>Session type</t>
   </si>
   <si>
-    <t>Match</t>
+    <t>e.g. Match</t>
   </si>
   <si>
     <t>My team color</t>
   </si>
   <si>
-    <t>black</t>
-  </si>
-  <si>
-    <t>Outfield jersey colour, lowercase</t>
+    <t>Outfield jersey colour, lowercase — e.g. black</t>
   </si>
   <si>
     <t>Opponent color</t>
   </si>
   <si>
-    <t>light blue</t>
+    <t>e.g. light blue</t>
   </si>
   <si>
     <t>My GK color</t>
   </si>
   <si>
-    <t>orange</t>
+    <t>e.g. orange</t>
   </si>
   <si>
     <t>Age group</t>
   </si>
   <si>
-    <t>U10</t>
+    <t>e.g. U10</t>
   </si>
   <si>
     <t>Video duration (MM:SS)</t>
   </si>
   <si>
-    <t>52:23</t>
+    <t>e.g. 52:23</t>
   </si>
   <si>
     <t>Final score — us</t>
   </si>
   <si>
+    <t>e.g. 4</t>
+  </si>
+  <si>
     <t>Final score — them</t>
+  </si>
+  <si>
+    <t>e.g. 1</t>
   </si>
   <si>
     <t>Us GK sub at (MM:SS)</t>
@@ -978,140 +972,164 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>36</v>
-      </c>
-      <c r="B3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>39</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
         <v>42</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
         <v>46</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>47</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>49</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>51</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>53</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1151,37 +1169,37 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>32</v>
@@ -1864,46 +1882,46 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="D1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>32</v>
@@ -2610,7 +2628,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2620,7 +2638,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2630,7 +2648,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -2638,7 +2656,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -2646,7 +2664,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -2654,7 +2672,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -2662,7 +2680,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
@@ -2670,7 +2688,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -2678,7 +2696,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
@@ -2686,7 +2704,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
@@ -2694,7 +2712,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2702,7 +2720,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
@@ -2710,37 +2728,37 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="D16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="J16" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="K16" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>32</v>
@@ -3434,31 +3452,31 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="D1" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>32</v>
@@ -4143,28 +4161,28 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="D1" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="H1" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>32</v>
@@ -4841,19 +4859,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>32</v>
